--- a/survey_templates/045_customer_support_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/045_customer_support_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_1</t>
+          <t>contact_reason</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What was the reason for your recent contact with our support team?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select a reason.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,23 +542,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_2</t>
+          <t>experience_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you rate your overall experience with our support team?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select a rating from 1 to 5.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_3</t>
+          <t>issue_resolution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Were you satisfied with the resolution of your issue?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please respond with a yes or no answer.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_4</t>
+          <t>email_notifications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Would you like to receive email notifications from our support team in the future?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select a preference.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_5</t>
+          <t>responsiveness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How would you rate the responsiveness of our support team?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rate from 1 to 5.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_6</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Do you have any additional feedback or suggestions for our support team?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_7</t>
+          <t>past_contact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Have you received any support from our team in the past?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please respond with a yes or no answer.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_8</t>
+          <t>main_issue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What was the main issue you contacted us about?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_9</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How did you feel about the communication from our support team during your recent contact?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate from 1 to 5.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,205 +758,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_10</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Would you recommend our support team to a friend or colleague?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select a preference.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>customer_support_feedback_survey</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,68 +821,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_4_choices</t>
+          <t>contact_reason_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_was_having_trouble_with_a_product/service.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I was having trouble with a product/service.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_4_choices</t>
+          <t>contact_reason_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_had_a_general_inquiry.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I had a general inquiry.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_5_choices</t>
+          <t>contact_reason_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_experienced_a_technical_issue.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I experienced a technical issue.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_support_feedback_survey_page_5_choices</t>
+          <t>contact_reason_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_needed_help_with_an_order.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I needed help with an order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>experience_rating_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1_-_very_poor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1 - Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>experience_rating_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2_-_poor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2 - Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>experience_rating_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3_-_neutral</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 - Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>experience_rating_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4_-_good</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4 - Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>experience_rating_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5_-_excellent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5 - Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>email_notifications_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>email_notifications_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>responsiveness_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1_-_very_slow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1 - Very Slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>responsiveness_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2_-_slow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2 - Slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>responsiveness_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3_-_average</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3 - Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>responsiveness_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4_-_fast</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4 - Fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>responsiveness_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5_-_extremely_fast</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5 - Extremely Fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1_-_very_poor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1 - Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2_-_poor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2 - Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3_-_neutral</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3 - Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4_-_good</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4 - Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5_-_excellent</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5 - Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>recommendation_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>recommendation_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
